--- a/Calendario-Camilo-Buenos-Aires.xlsx
+++ b/Calendario-Camilo-Buenos-Aires.xlsx
@@ -9,7 +9,464 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>hora</t>
+  </si>
+  <si>
+    <t>momento</t>
+  </si>
+  <si>
+    <t>titulo</t>
+  </si>
+  <si>
+    <t>zona</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>sorpresa</t>
+  </si>
+  <si>
+    <t>desbloqueo</t>
+  </si>
+  <si>
+    <t>pista</t>
+  </si>
+  <si>
+    <t>fila_para_html</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>Llegada</t>
+  </si>
+  <si>
+    <t>Llegada a Buenos Aires</t>
+  </si>
+  <si>
+    <t>Ezeiza / Adrogue</t>
+  </si>
+  <si>
+    <t>Llegada besos abrazos descanso y cositas hot.</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>2026-09-12T05:00:00-03:00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-09-12|05:00|Llegada|Llegada a Buenos Aires|Ezeiza / Adrogue|Llegada besos abrazos descanso y cositas hot.|no|2026-09-12T05:00:00-03:00|</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>Noche</t>
+  </si>
+  <si>
+    <t>Primera inmersion argentina</t>
+  </si>
+  <si>
+    <t>Adrogue</t>
+  </si>
+  <si>
+    <t>Una noche para entender mejor el pais costumbres historia palabras futbol comida y codigos argentinos.</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>2026-09-12T18:00:00-03:00</t>
+  </si>
+  <si>
+    <t>cultura-argentina</t>
+  </si>
+  <si>
+    <t>2026-09-12|21:00|Noche|Primera inmersion argentina|Adrogue|Una noche para entender mejor el pais costumbres historia palabras futbol comida y codigos argentinos.|si|2026-09-12T18:00:00-03:00|cultura-argentina</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>Manana</t>
+  </si>
+  <si>
+    <t>La casa azul y oro</t>
+  </si>
+  <si>
+    <t>La Boca</t>
+  </si>
+  <si>
+    <t>Plan futbolero para conocer uno de los lugares mas intensos de Buenos Aires.</t>
+  </si>
+  <si>
+    <t>2026-09-13T08:00:00-03:00</t>
+  </si>
+  <si>
+    <t>azul-oro</t>
+  </si>
+  <si>
+    <t>2026-09-13|10:00|Manana|La casa azul y oro|La Boca|Plan futbolero para conocer uno de los lugares mas intensos de Buenos Aires.|si|2026-09-13T08:00:00-03:00|azul-oro</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>Tarde</t>
+  </si>
+  <si>
+    <t>La aguja blanca</t>
+  </si>
+  <si>
+    <t>Centro de Buenos Aires</t>
+  </si>
+  <si>
+    <t>Un clasico porteno en una avenida imposible de ignorar.</t>
+  </si>
+  <si>
+    <t>2026-09-13T09:00:00-03:00</t>
+  </si>
+  <si>
+    <t>aguja-blanca</t>
+  </si>
+  <si>
+    <t>2026-09-13|14:30|Tarde|La aguja blanca|Centro de Buenos Aires|Un clasico porteno en una avenida imposible de ignorar.|si|2026-09-13T09:00:00-03:00|aguja-blanca</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>Balcones plaza y piedra antigua</t>
+  </si>
+  <si>
+    <t>Plaza de Mayo</t>
+  </si>
+  <si>
+    <t>Recorrido por Plaza de Mayo Casa Rosada y Cabildo.</t>
+  </si>
+  <si>
+    <t>2026-09-13T09:30:00-03:00</t>
+  </si>
+  <si>
+    <t>plaza-memoria</t>
+  </si>
+  <si>
+    <t>2026-09-13|15:30|Tarde|Balcones plaza y piedra antigua|Plaza de Mayo|Recorrido por Plaza de Mayo Casa Rosada y Cabildo.|si|2026-09-13T09:30:00-03:00|plaza-memoria</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>Una fachada que canta</t>
+  </si>
+  <si>
+    <t>Pasada por uno de los teatros mas famosos del mundo.</t>
+  </si>
+  <si>
+    <t>2026-09-13T10:00:00-03:00</t>
+  </si>
+  <si>
+    <t>fachada-canta</t>
+  </si>
+  <si>
+    <t>2026-09-13|17:00|Tarde|Una fachada que canta|Centro de Buenos Aires|Pasada por uno de los teatros mas famosos del mundo.|si|2026-09-13T10:00:00-03:00|fachada-canta</t>
+  </si>
+  <si>
+    <t>Ocho pasos sin decirlo</t>
+  </si>
+  <si>
+    <t>A confirmar</t>
+  </si>
+  <si>
+    <t>Una noche donde la ciudad cuenta historias con el cuerpo y la musica.</t>
+  </si>
+  <si>
+    <t>2026-09-13T12:00:00-03:00</t>
+  </si>
+  <si>
+    <t>ocho-compases</t>
+  </si>
+  <si>
+    <t>2026-09-13|21:00|Noche|Ocho pasos sin decirlo|A confirmar|Una noche donde la ciudad cuenta historias con el cuerpo y la musica.|si|2026-09-13T12:00:00-03:00|ocho-compases</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>Mapa entre dos panes</t>
+  </si>
+  <si>
+    <t>Danke</t>
+  </si>
+  <si>
+    <t>Una hamburgueseria con sabores viajeros y nombres de paises.</t>
+  </si>
+  <si>
+    <t>2026-09-14T10:00:00-03:00</t>
+  </si>
+  <si>
+    <t>mapa-pan</t>
+  </si>
+  <si>
+    <t>2026-09-14|20:30|Noche|Mapa entre dos panes|Danke|Una hamburgueseria con sabores viajeros y nombres de paises.|si|2026-09-14T10:00:00-03:00|mapa-pan</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>Postre</t>
+  </si>
+  <si>
+    <t>Frio dulce en palito</t>
+  </si>
+  <si>
+    <t>Lucciano's</t>
+  </si>
+  <si>
+    <t>Una parada de postre que ya estaba prometida pero igual suma emocion.</t>
+  </si>
+  <si>
+    <t>2026-09-14T12:00:00-03:00</t>
+  </si>
+  <si>
+    <t>frio-palito</t>
+  </si>
+  <si>
+    <t>2026-09-14|22:00|Postre|Frio dulce en palito|Lucciano's|Una parada de postre que ya estaba prometida pero igual suma emocion.|si|2026-09-14T12:00:00-03:00|frio-palito</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>Diez esperando caer</t>
+  </si>
+  <si>
+    <t>Un juego de punteria ruido y zapatos raros.</t>
+  </si>
+  <si>
+    <t>2026-09-15T10:00:00-03:00</t>
+  </si>
+  <si>
+    <t>diez-caen</t>
+  </si>
+  <si>
+    <t>2026-09-15|19:00|Noche|Diez esperando caer|A confirmar|Un juego de punteria ruido y zapatos raros.|si|2026-09-15T10:00:00-03:00|diez-caen</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>Dia</t>
+  </si>
+  <si>
+    <t>Humo brasas y amigos</t>
+  </si>
+  <si>
+    <t>Cerca de Adrogue</t>
+  </si>
+  <si>
+    <t>Asado con amigos cerca de casa.</t>
+  </si>
+  <si>
+    <t>2026-09-16T09:00:00-03:00</t>
+  </si>
+  <si>
+    <t>brasas-amigos</t>
+  </si>
+  <si>
+    <t>2026-09-16|12:30|Dia|Humo brasas y amigos|Cerca de Adrogue|Asado con amigos cerca de casa.|si|2026-09-16T09:00:00-03:00|brasas-amigos</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>Copas con acento mendocino</t>
+  </si>
+  <si>
+    <t>Un momento para probar vinos y descubrir sabores argentinos.</t>
+  </si>
+  <si>
+    <t>2026-09-16T12:00:00-03:00</t>
+  </si>
+  <si>
+    <t>uvas-copa</t>
+  </si>
+  <si>
+    <t>2026-09-16|20:00|Noche|Copas con acento mendocino|Adrogue|Un momento para probar vinos y descubrir sabores argentinos.|si|2026-09-16T12:00:00-03:00|uvas-copa</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>Entrar en otra escena</t>
+  </si>
+  <si>
+    <t>Tal vez cine o una experiencia inmersiva para hacer algo distinto.</t>
+  </si>
+  <si>
+    <t>2026-09-17T10:00:00-03:00</t>
+  </si>
+  <si>
+    <t>otra-escena</t>
+  </si>
+  <si>
+    <t>2026-09-17|19:00|Noche|Entrar en otra escena|A confirmar|Tal vez cine o una experiencia inmersiva para hacer algo distinto.|si|2026-09-17T10:00:00-03:00|otra-escena</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>Mesa celeste y blanca</t>
+  </si>
+  <si>
+    <t>Juntada tematica argentina con mis amigos.</t>
+  </si>
+  <si>
+    <t>2026-09-18T09:00:00-03:00</t>
+  </si>
+  <si>
+    <t>mesa-celeste</t>
+  </si>
+  <si>
+    <t>2026-09-18|20:30|Noche|Mesa celeste y blanca|Adrogue|Juntada tematica argentina con mis amigos.|si|2026-09-18T09:00:00-03:00|mesa-celeste</t>
+  </si>
+  <si>
+    <t>Dulce</t>
+  </si>
+  <si>
+    <t>Copa de capas dulces</t>
+  </si>
+  <si>
+    <t>Un mundial muy serio de algo redondo dulce y argentino.</t>
+  </si>
+  <si>
+    <t>2026-09-18T12:00:00-03:00</t>
+  </si>
+  <si>
+    <t>capas-dulces</t>
+  </si>
+  <si>
+    <t>2026-09-18|22:00|Dulce|Copa de capas dulces|Adrogue|Un mundial muy serio de algo redondo dulce y argentino.|si|2026-09-18T12:00:00-03:00|capas-dulces</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>Un portal a otra ciudad</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Arcos sabores nuevos y calles llenas de colores.</t>
+  </si>
+  <si>
+    <t>2026-09-19T09:00:00-03:00</t>
+  </si>
+  <si>
+    <t>portal-sabores</t>
+  </si>
+  <si>
+    <t>2026-09-19|13:00|Tarde|Un portal a otra ciudad|Belgrano|Arcos sabores nuevos y calles llenas de colores.|si|2026-09-19T09:00:00-03:00|portal-sabores</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>Parada al norte</t>
+  </si>
+  <si>
+    <t>Nunez</t>
+  </si>
+  <si>
+    <t>Una vuelta por una zona al norte de la ciudad.</t>
+  </si>
+  <si>
+    <t>2026-09-19T11:00:00-03:00</t>
+  </si>
+  <si>
+    <t>norte-rio</t>
+  </si>
+  <si>
+    <t>2026-09-19|18:30|Tarde|Parada al norte|Nunez|Una vuelta por una zona al norte de la ciudad.|si|2026-09-19T11:00:00-03:00|norte-rio</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>Despedida tranquila</t>
+  </si>
+  <si>
+    <t>Llorar mucho 😭😭 repasar historias y preparar el regreso.</t>
+  </si>
+  <si>
+    <t>2026-09-20T09:00:00-03:00</t>
+  </si>
+  <si>
+    <t>2026-09-20|12:00|Dia|Despedida tranquila|Adrogue|Llorar mucho 😭😭 repasar historias y preparar el regreso.|no|2026-09-20T09:00:00-03:00|</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>Viaje de regreso</t>
+  </si>
+  <si>
+    <t>Adrogue / Aeropuerto</t>
+  </si>
+  <si>
+    <t>Cierre del viaje y vuelta a casa.</t>
+  </si>
+  <si>
+    <t>2026-09-20T20:00:00-03:00</t>
+  </si>
+  <si>
+    <t>2026-09-21|08:00|Dia|Viaje de regreso|Adrogue / Aeropuerto|Cierre del viaje y vuelta a casa.|no|2026-09-20T20:00:00-03:00|</t>
+  </si>
+  <si>
+    <t>Editá la hoja Calendario.</t>
+  </si>
+  <si>
+    <t>La última columna fila_para_html se copia al bloque ITINERARY_CSV del HTML.</t>
+  </si>
+  <si>
+    <t>Esta app no sincroniza sola porque es HTML puro.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17,7 +474,6 @@
   <fonts count="2">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -37,25 +493,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF102A56"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -64,18 +513,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:J20"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
     <col min="10" max="10" width="70" customWidth="1"/>
   </cols>
   <sheetData>
@@ -163,560 +612,560 @@
         <v>24</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>23</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J13" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I14" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J14" t="s" s="0">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>23</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J15" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>23</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J16" t="s" s="0">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J17" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G18" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J18" t="s" s="0">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>23</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" t="s" s="0">
         <v>16</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>18</v>
       </c>
       <c r="J19" t="s" s="0">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G20" t="s" s="0">
         <v>16</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I20" t="s" s="0">
         <v>18</v>
       </c>
       <c r="J20" t="s" s="0">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -725,57 +1174,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A3"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="1" max="1" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
         <v>151</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>156</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:A3"/>
 </worksheet>
 </file>